--- a/artfynd/A 56697-2023 artfynd.xlsx
+++ b/artfynd/A 56697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,6 +3033,134 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124690011</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Helgum, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>590342</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7007018</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56697-2023 artfynd.xlsx
+++ b/artfynd/A 56697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,6 +3161,134 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124690133</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Helgum, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>590552</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7007181</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56697-2023 artfynd.xlsx
+++ b/artfynd/A 56697-2023 artfynd.xlsx
@@ -3038,7 +3038,7 @@
         <v>124690011</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>124690133</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 56697-2023 artfynd.xlsx
+++ b/artfynd/A 56697-2023 artfynd.xlsx
@@ -3166,12 +3166,7 @@
         <v>124690133</v>
       </c>
       <c r="B26" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
